--- a/excel/butterScaler/butterScaler23-Section02.xlsx
+++ b/excel/butterScaler/butterScaler23-Section02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559509C5-8734-754B-837A-9CBE77A7B733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B199E86F-BDB8-3A4F-B925-3C4FCEFD2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5600" yWindow="-26760" windowWidth="28340" windowHeight="18840" xr2:uid="{BAFFE9DA-3B16-ED42-8F62-B38F2EE3FAD2}"/>
+    <workbookView xWindow="-12200" yWindow="-28200" windowWidth="27580" windowHeight="28200" xr2:uid="{BAFFE9DA-3B16-ED42-8F62-B38F2EE3FAD2}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
   <si>
     <t>ActionName</t>
   </si>
@@ -62,248 +62,248 @@
     <t>站姿准备</t>
   </si>
   <si>
-    <t>中等站距准备</t>
-  </si>
-  <si>
-    <t>双脚在髋外侧，弹力带膝盖上方</t>
-  </si>
-  <si>
-    <t>第2个8拍，保持准备姿势</t>
-  </si>
-  <si>
-    <t>第3个8拍，保持准备姿势</t>
-  </si>
-  <si>
-    <t>第4个8拍，保持准备姿势</t>
-  </si>
-  <si>
-    <t>后抬腿</t>
-  </si>
-  <si>
-    <t>2/2后抬腿</t>
-  </si>
-  <si>
-    <t>左腿后抬，2拍完成</t>
-  </si>
-  <si>
-    <t>右腿后抬，2拍完成</t>
-  </si>
-  <si>
-    <t>保持稳定</t>
-  </si>
-  <si>
-    <t>左右交替，控制节奏</t>
-  </si>
-  <si>
-    <t>保持动作</t>
-  </si>
-  <si>
-    <t>准备变速</t>
-  </si>
-  <si>
-    <t>慢速后抬腿</t>
-  </si>
-  <si>
-    <t>2p/s慢速后抬腿</t>
-  </si>
-  <si>
-    <t>慢速启动</t>
-  </si>
-  <si>
-    <t>2拍一次，左腿后抬</t>
-  </si>
-  <si>
-    <t>慢速进行</t>
-  </si>
-  <si>
-    <t>2拍一次，右腿后抬</t>
-  </si>
-  <si>
-    <t>感受控制</t>
-  </si>
-  <si>
-    <t>慢速模式，肌肉收缩</t>
-  </si>
-  <si>
-    <t>保持慢速</t>
-  </si>
-  <si>
-    <t>准备加速切换</t>
-  </si>
-  <si>
-    <t>快速后抬腿</t>
-  </si>
-  <si>
-    <t>3p/s快速后抬腿</t>
-  </si>
-  <si>
-    <t>加速开始</t>
-  </si>
-  <si>
-    <t>3拍一次，左腿快速</t>
-  </si>
-  <si>
-    <t>快速进行</t>
-  </si>
-  <si>
-    <t>3拍一次，右腿快速</t>
-  </si>
-  <si>
-    <t>跟上节奏</t>
-  </si>
-  <si>
-    <t>高频模式，保持频率</t>
-  </si>
-  <si>
-    <t>保持快速</t>
-  </si>
-  <si>
-    <t>准备换动作</t>
-  </si>
-  <si>
-    <t>螃蟹步</t>
-  </si>
-  <si>
-    <t>2/2螃蟹步</t>
-  </si>
-  <si>
-    <t>螃蟹步开始</t>
-  </si>
-  <si>
-    <t>侧移2次，每步4拍</t>
-  </si>
-  <si>
-    <t>左右移动</t>
-  </si>
-  <si>
-    <t>左侧两步，右侧两步</t>
-  </si>
-  <si>
-    <t>保持节奏</t>
-  </si>
-  <si>
-    <t>横向移动，2次完成</t>
-  </si>
-  <si>
-    <t>动作稳定</t>
-  </si>
-  <si>
-    <t>准备减速切换</t>
-  </si>
-  <si>
-    <t>慢速腿外展</t>
-  </si>
-  <si>
-    <t>2p/s慢速腿外展</t>
-  </si>
-  <si>
-    <t>慢速外展</t>
-  </si>
-  <si>
-    <t>2拍一次，左腿侧抬</t>
-  </si>
-  <si>
-    <t>2拍一次，右腿侧抬</t>
-  </si>
-  <si>
-    <t>核心收紧</t>
-  </si>
-  <si>
-    <t>侧向控制，保持平衡</t>
-  </si>
-  <si>
-    <t>快速腿外展</t>
-  </si>
-  <si>
-    <t>3p/s快速腿外展</t>
-  </si>
-  <si>
-    <t>快速外展</t>
-  </si>
-  <si>
-    <t>3拍一次，左腿快速侧抬</t>
-  </si>
-  <si>
-    <t>3拍一次，右腿快速侧抬</t>
-  </si>
-  <si>
-    <t>高频动作</t>
-  </si>
-  <si>
-    <t>跟上节奏，保持频率</t>
-  </si>
-  <si>
-    <t>保持速度</t>
-  </si>
-  <si>
-    <t>准备超级加速</t>
-  </si>
-  <si>
-    <t>超级快速腿外展</t>
-  </si>
-  <si>
-    <t>7p/s超级快速腿外展</t>
-  </si>
-  <si>
-    <t>极限加速</t>
-  </si>
-  <si>
-    <t>7拍一次，最快速度</t>
-  </si>
-  <si>
-    <t>超级快速</t>
-  </si>
-  <si>
-    <t>高频外展，极限挑战</t>
-  </si>
-  <si>
-    <t>保持极限</t>
-  </si>
-  <si>
-    <t>最高频率，坚持住</t>
-  </si>
-  <si>
-    <t>最后冲刺</t>
-  </si>
-  <si>
-    <t>准备螃蟹步收尾</t>
-  </si>
-  <si>
-    <t>快速螃蟹步</t>
-  </si>
-  <si>
-    <t>快速启动</t>
-  </si>
-  <si>
-    <t>4次移动，每步1拍</t>
-  </si>
-  <si>
-    <t>最快速度</t>
-  </si>
-  <si>
-    <t>快速横移，高频踏步</t>
-  </si>
-  <si>
-    <t>冲刺阶段</t>
-  </si>
-  <si>
-    <t>保持极速，左右快移</t>
-  </si>
-  <si>
-    <t>课程即将结束</t>
-  </si>
-  <si>
-    <t>结束</t>
-  </si>
-  <si>
     <t>StepActionName</t>
+  </si>
+  <si>
+    <t>脚后跟踩在髋的外侧</t>
+  </si>
+  <si>
+    <t>脚尖微微向外</t>
+  </si>
+  <si>
+    <t>屈膝屈髋</t>
+  </si>
+  <si>
+    <t>站姿后抬腿</t>
+  </si>
+  <si>
+    <t>Two and Two</t>
+  </si>
+  <si>
+    <t>勾脚尖</t>
+  </si>
+  <si>
+    <t>整条腿向斜后上方</t>
+  </si>
+  <si>
+    <t>抬高30-45度</t>
+  </si>
+  <si>
+    <t>再来一边一次</t>
+  </si>
+  <si>
+    <t>准备加快</t>
+  </si>
+  <si>
+    <t>向后向上</t>
+  </si>
+  <si>
+    <t>一边2次向后向上</t>
+  </si>
+  <si>
+    <t>1边2次后抬腿</t>
+  </si>
+  <si>
+    <t>右侧2次后抬腿</t>
+  </si>
+  <si>
+    <t>左侧2次后抬腿</t>
+  </si>
+  <si>
+    <t>右侧1次后抬腿</t>
+  </si>
+  <si>
+    <t>左侧1次后抬腿</t>
+  </si>
+  <si>
+    <t>支撑腿保持微屈</t>
+  </si>
+  <si>
+    <t>放松</t>
+  </si>
+  <si>
+    <t>肚子绷紧</t>
+  </si>
+  <si>
+    <t>让我们的髋保持水平</t>
+  </si>
+  <si>
+    <t>还有1边1组</t>
+  </si>
+  <si>
+    <t>连续3次弹动</t>
+  </si>
+  <si>
+    <t>Ready</t>
+  </si>
+  <si>
+    <t>Ready, Here we go</t>
+  </si>
+  <si>
+    <t>1次后抬腿</t>
+  </si>
+  <si>
+    <t>2次后抬腿</t>
+  </si>
+  <si>
+    <t>3次后抬腿</t>
+  </si>
+  <si>
+    <t>右侧3次后抬腿</t>
+  </si>
+  <si>
+    <t>左侧3次后抬腿</t>
+  </si>
+  <si>
+    <t>小幅度向后向上</t>
+  </si>
+  <si>
+    <t>收紧臀腿后侧</t>
+  </si>
+  <si>
+    <t>最后一组</t>
+  </si>
+  <si>
+    <t>准备新动作</t>
+  </si>
+  <si>
+    <t>向右2次慢速螃蟹步</t>
+  </si>
+  <si>
+    <t>向右2次螃蟹步</t>
+  </si>
+  <si>
+    <t>2次螃蟹步</t>
+  </si>
+  <si>
+    <t>向左2次螃蟹步</t>
+  </si>
+  <si>
+    <t>移动一个脚掌的距离</t>
+  </si>
+  <si>
+    <t>让我们膝盖向外对齐脚尖</t>
+  </si>
+  <si>
+    <t>保持弹力绳紧绷</t>
+  </si>
+  <si>
+    <t>微微俯身</t>
+  </si>
+  <si>
+    <t>注意力放在臀部的外侧</t>
+  </si>
+  <si>
+    <t>再来一次</t>
+  </si>
+  <si>
+    <t>回到原地</t>
+  </si>
+  <si>
+    <t>腿外展，右腿向外</t>
+  </si>
+  <si>
+    <t>2次腿外展</t>
+  </si>
+  <si>
+    <t>向右2次腿外展</t>
+  </si>
+  <si>
+    <t>向左2次腿外展</t>
+  </si>
+  <si>
+    <t>把肚子收紧一点</t>
+  </si>
+  <si>
+    <t>肩膀和髋水平</t>
+  </si>
+  <si>
+    <t>收紧臀腿的外侧</t>
+  </si>
+  <si>
+    <t>准备加快一点</t>
+  </si>
+  <si>
+    <t>3次腿外展</t>
+  </si>
+  <si>
+    <t>向右3次腿外展</t>
+  </si>
+  <si>
+    <t>向左3次腿外展</t>
+  </si>
+  <si>
+    <t>3，2，1</t>
+  </si>
+  <si>
+    <t>非常好</t>
+  </si>
+  <si>
+    <t>屁股外侧很有感觉了哈</t>
+  </si>
+  <si>
+    <t>当然你可以选择脚尖抬离地板</t>
+  </si>
+  <si>
+    <t>小幅度再来一边一次</t>
+  </si>
+  <si>
+    <t>接下来从3次来到7次</t>
+  </si>
+  <si>
+    <t>7次腿外展</t>
+  </si>
+  <si>
+    <t>向右7次腿外展</t>
+  </si>
+  <si>
+    <t>向左7次腿外展</t>
+  </si>
+  <si>
+    <t>1，2，3，4</t>
+  </si>
+  <si>
+    <t>5，6，7</t>
+  </si>
+  <si>
+    <t>整个身体向上挺拔</t>
+  </si>
+  <si>
+    <t>One More</t>
+  </si>
+  <si>
+    <t>准备加快，4次螃蟹步</t>
+  </si>
+  <si>
+    <t>4次螃蟹步</t>
+  </si>
+  <si>
+    <t>向右4次螃蟹步</t>
+  </si>
+  <si>
+    <t>向左4次螃蟹步</t>
+  </si>
+  <si>
+    <t>双脚贴地滑行</t>
+  </si>
+  <si>
+    <t>让脚掌的外侧压住地板</t>
+  </si>
+  <si>
+    <t>再一次刺激整个臀部外侧</t>
+  </si>
+  <si>
+    <t>再来最后一轮</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -443,6 +443,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -786,12 +793,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1188,7 +1196,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1225,9 +1233,6 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" t="b">
         <v>0</v>
       </c>
@@ -1249,9 +1254,6 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="b">
@@ -1275,9 +1277,6 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="b">
@@ -1301,16 +1300,16 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1318,22 +1317,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6">
-        <v>4321</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1344,22 +1340,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7">
-        <v>4321</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1370,22 +1363,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
         <v>15</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>1212</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1396,19 +1386,19 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>4</v>
       </c>
-      <c r="E9">
-        <v>123</v>
+      <c r="E9" t="s">
+        <v>16</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
@@ -1422,22 +1412,19 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10">
-        <v>1234567</v>
-      </c>
-      <c r="F10" t="s">
-        <v>19</v>
+      <c r="E10" t="s">
+        <v>20</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -1448,22 +1435,16 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>4</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" t="s">
-        <v>19</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -1474,22 +1455,19 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B12">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -1500,19 +1478,19 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
         <v>21</v>
@@ -1521,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1529,7 +1507,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -1540,11 +1518,8 @@
       <c r="D14">
         <v>4</v>
       </c>
-      <c r="E14" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" t="s">
-        <v>25</v>
+      <c r="E14">
+        <v>1221</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -1555,22 +1530,19 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" t="s">
-        <v>25</v>
+      <c r="E15">
+        <v>1221</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -1581,7 +1553,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B16">
         <v>8</v>
@@ -1593,10 +1565,10 @@
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -1607,22 +1579,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -1633,7 +1602,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B18">
         <v>8</v>
@@ -1645,10 +1614,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -1659,22 +1625,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B19">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -1685,7 +1648,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B20">
         <v>8</v>
@@ -1697,10 +1660,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -1711,28 +1671,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B21">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -1740,22 +1700,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B22">
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
@@ -1766,22 +1723,19 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B23">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
@@ -1792,22 +1746,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B24">
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D24">
         <v>4</v>
-      </c>
-      <c r="E24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" t="s">
-        <v>37</v>
       </c>
       <c r="G24" t="b">
         <v>0</v>
@@ -1818,22 +1766,19 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B25">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
@@ -1844,22 +1789,19 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -1870,22 +1812,19 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B27">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
-      </c>
-      <c r="F27" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
@@ -1896,22 +1835,19 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
@@ -1922,28 +1858,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" t="s">
         <v>33</v>
-      </c>
-      <c r="B29">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29" t="s">
-        <v>40</v>
-      </c>
-      <c r="F29" t="s">
-        <v>41</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -1951,22 +1887,19 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B30">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
-      <c r="E30" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" t="s">
-        <v>45</v>
+      <c r="E30">
+        <v>1221</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -1977,22 +1910,19 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B31">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -2003,22 +1933,19 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B32">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
-      </c>
-      <c r="F32" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -2029,22 +1956,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B33">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
@@ -2055,22 +1979,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B34">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -2081,22 +2002,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
@@ -2107,22 +2025,19 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B36">
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>50</v>
-      </c>
-      <c r="F36" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -2133,28 +2048,28 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B37">
         <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -2162,22 +2077,19 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B38">
         <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>4</v>
       </c>
-      <c r="E38" t="s">
-        <v>54</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
+      <c r="E38">
+        <v>1221</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
@@ -2188,22 +2100,19 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
-      <c r="E39" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
+      <c r="E39">
+        <v>1221</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
@@ -2214,22 +2123,16 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B40">
         <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>4</v>
-      </c>
-      <c r="E40" t="s">
-        <v>26</v>
-      </c>
-      <c r="F40" t="s">
-        <v>56</v>
       </c>
       <c r="G40" t="b">
         <v>0</v>
@@ -2240,22 +2143,19 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B41">
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D41">
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
@@ -2266,22 +2166,19 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B42">
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
@@ -2292,22 +2189,19 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B43">
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
-      </c>
-      <c r="F43" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -2318,22 +2212,22 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
         <v>53</v>
       </c>
-      <c r="B44">
-        <v>8</v>
-      </c>
-      <c r="C44" t="s">
-        <v>53</v>
-      </c>
-      <c r="D44">
-        <v>4</v>
-      </c>
-      <c r="E44" t="s">
-        <v>30</v>
-      </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
@@ -2344,28 +2238,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B45">
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -2373,22 +2264,19 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B46">
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D46">
         <v>4</v>
       </c>
-      <c r="E46" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
+      <c r="E46" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
@@ -2399,22 +2287,19 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B47">
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D47">
         <v>4</v>
       </c>
-      <c r="E47" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
+      <c r="E47" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
@@ -2425,22 +2310,19 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B48">
         <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D48">
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -2451,22 +2333,19 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B49">
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
@@ -2477,22 +2356,19 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B50">
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
@@ -2503,22 +2379,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B51">
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D51">
         <v>4</v>
-      </c>
-      <c r="E51" t="s">
-        <v>64</v>
-      </c>
-      <c r="F51" t="s">
-        <v>65</v>
       </c>
       <c r="G51" t="b">
         <v>0</v>
@@ -2529,22 +2399,19 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B52">
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>66</v>
-      </c>
-      <c r="F52" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -2555,28 +2422,25 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B53">
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D53">
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>66</v>
-      </c>
-      <c r="F53" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -2584,22 +2448,19 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B54">
         <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>70</v>
-      </c>
-      <c r="F54" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
@@ -2610,22 +2471,22 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B55">
         <v>4</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D55">
         <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F55" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
@@ -2636,22 +2497,19 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B56">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>74</v>
-      </c>
-      <c r="F56" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
@@ -2662,28 +2520,25 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>76</v>
-      </c>
-      <c r="F57" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -2691,19 +2546,19 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B58">
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D58">
         <v>4</v>
       </c>
-      <c r="E58" t="s">
-        <v>79</v>
+      <c r="E58">
+        <v>1234</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
@@ -2714,19 +2569,19 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B59">
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
-      <c r="E59" t="s">
-        <v>80</v>
+      <c r="E59">
+        <v>4321</v>
       </c>
       <c r="G59" t="b">
         <v>0</v>
@@ -2737,19 +2592,19 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B60">
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D60">
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -2760,19 +2615,19 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B61">
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
@@ -2783,19 +2638,19 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B62">
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D62">
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
@@ -2806,19 +2661,19 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B63">
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D63">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
@@ -2829,19 +2684,19 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B64">
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D64">
         <v>4</v>
       </c>
-      <c r="E64" t="s">
-        <v>76</v>
+      <c r="E64">
+        <v>1234</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
@@ -2852,25 +2707,25 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B65">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D65">
         <v>4</v>
       </c>
-      <c r="E65" t="s">
-        <v>85</v>
+      <c r="E65">
+        <v>4321</v>
+      </c>
+      <c r="F65" t="s">
+        <v>87</v>
       </c>
       <c r="G65" t="b">
-        <v>1</v>
-      </c>
-      <c r="H65" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>

--- a/excel/butterScaler/butterScaler23-Section02.xlsx
+++ b/excel/butterScaler/butterScaler23-Section02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B199E86F-BDB8-3A4F-B925-3C4FCEFD2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0EBDD5-B6DE-F54C-BF72-E76D926122CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-12200" yWindow="-28200" windowWidth="27580" windowHeight="28200" xr2:uid="{BAFFE9DA-3B16-ED42-8F62-B38F2EE3FAD2}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
   <si>
     <t>ActionName</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>一边2次向后向上</t>
-  </si>
-  <si>
-    <t>1边2次后抬腿</t>
   </si>
   <si>
     <t>右侧2次后抬腿</t>
@@ -1309,7 +1306,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1317,13 +1314,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -1340,13 +1337,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -1363,13 +1360,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -1386,13 +1383,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1412,13 +1409,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -1435,13 +1432,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -1455,13 +1452,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -1478,13 +1475,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -1499,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1507,13 +1504,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
         <v>22</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>23</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -1530,13 +1527,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B15">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1553,22 +1550,22 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
         <v>27</v>
-      </c>
-      <c r="F16" t="s">
-        <v>28</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -1579,19 +1576,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -1602,19 +1599,19 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -1625,19 +1622,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19">
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -1648,13 +1645,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1671,28 +1668,28 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -1700,19 +1697,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
         <v>37</v>
       </c>
-      <c r="B22">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
@@ -1723,19 +1720,19 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
@@ -1746,13 +1743,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
         <v>37</v>
-      </c>
-      <c r="B24">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -1766,19 +1763,19 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
         <v>39</v>
-      </c>
-      <c r="D25">
-        <v>4</v>
-      </c>
-      <c r="E25" t="s">
-        <v>40</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
@@ -1789,19 +1786,19 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
         <v>37</v>
       </c>
-      <c r="B26">
-        <v>8</v>
-      </c>
-      <c r="C26" t="s">
-        <v>38</v>
-      </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -1812,19 +1809,19 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
@@ -1835,19 +1832,19 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
         <v>37</v>
       </c>
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
-        <v>38</v>
-      </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
@@ -1858,28 +1855,28 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29">
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -1887,13 +1884,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -1910,19 +1907,19 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
         <v>46</v>
       </c>
-      <c r="B31">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31" t="s">
         <v>47</v>
-      </c>
-      <c r="D31">
-        <v>4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -1933,19 +1930,19 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32">
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -1956,19 +1953,19 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
         <v>46</v>
       </c>
-      <c r="B33">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>47</v>
-      </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G33" t="b">
         <v>0</v>
@@ -1979,19 +1976,19 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D34">
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -2002,19 +1999,19 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
         <v>46</v>
       </c>
-      <c r="B35">
-        <v>8</v>
-      </c>
-      <c r="C35" t="s">
-        <v>47</v>
-      </c>
       <c r="D35">
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
@@ -2025,19 +2022,19 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36">
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -2048,28 +2045,28 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
         <v>46</v>
       </c>
-      <c r="B37">
-        <v>8</v>
-      </c>
-      <c r="C37" t="s">
-        <v>47</v>
-      </c>
       <c r="D37">
         <v>4</v>
       </c>
       <c r="E37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" t="s">
         <v>54</v>
-      </c>
-      <c r="F37" t="s">
-        <v>55</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -2077,13 +2074,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
         <v>56</v>
-      </c>
-      <c r="B38">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
-        <v>57</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -2100,13 +2097,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -2123,13 +2120,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
         <v>56</v>
-      </c>
-      <c r="B40">
-        <v>8</v>
-      </c>
-      <c r="C40" t="s">
-        <v>57</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -2143,19 +2140,19 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41">
         <v>8</v>
       </c>
       <c r="C41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
         <v>58</v>
-      </c>
-      <c r="D41">
-        <v>4</v>
-      </c>
-      <c r="E41" t="s">
-        <v>59</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
@@ -2166,19 +2163,19 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
         <v>56</v>
       </c>
-      <c r="B42">
-        <v>8</v>
-      </c>
-      <c r="C42" t="s">
-        <v>57</v>
-      </c>
       <c r="D42">
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G42" t="b">
         <v>0</v>
@@ -2189,19 +2186,19 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -2212,22 +2209,22 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
         <v>56</v>
       </c>
-      <c r="B44">
-        <v>8</v>
-      </c>
-      <c r="C44" t="s">
-        <v>57</v>
-      </c>
       <c r="D44">
         <v>4</v>
       </c>
       <c r="E44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
@@ -2238,25 +2235,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B45">
         <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D45">
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G45" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I45" t="b">
         <v>0</v>
@@ -2264,19 +2261,19 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
         <v>63</v>
       </c>
-      <c r="B46">
-        <v>8</v>
-      </c>
-      <c r="C46" t="s">
-        <v>64</v>
-      </c>
       <c r="D46">
         <v>4</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
@@ -2287,19 +2284,19 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B47">
         <v>8</v>
       </c>
       <c r="C47" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="G47" t="b">
         <v>0</v>
@@ -2310,19 +2307,19 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
         <v>63</v>
       </c>
-      <c r="B48">
-        <v>8</v>
-      </c>
-      <c r="C48" t="s">
-        <v>64</v>
-      </c>
       <c r="D48">
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -2333,19 +2330,19 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B49">
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D49">
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
@@ -2356,19 +2353,19 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
         <v>63</v>
       </c>
-      <c r="B50">
-        <v>8</v>
-      </c>
-      <c r="C50" t="s">
-        <v>64</v>
-      </c>
       <c r="D50">
         <v>4</v>
       </c>
       <c r="E50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
@@ -2379,13 +2376,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51">
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -2399,19 +2396,19 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
         <v>63</v>
       </c>
-      <c r="B52">
-        <v>8</v>
-      </c>
-      <c r="C52" t="s">
-        <v>64</v>
-      </c>
       <c r="D52">
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -2422,25 +2419,25 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B53">
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D53">
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G53" t="b">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -2448,19 +2445,19 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
         <v>72</v>
       </c>
-      <c r="B54">
-        <v>4</v>
-      </c>
-      <c r="C54" t="s">
-        <v>73</v>
-      </c>
       <c r="D54">
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
@@ -2471,22 +2468,22 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
         <v>72</v>
       </c>
-      <c r="B55">
-        <v>4</v>
-      </c>
-      <c r="C55" t="s">
-        <v>73</v>
-      </c>
       <c r="D55">
         <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G55" t="b">
         <v>0</v>
@@ -2497,19 +2494,19 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B56">
         <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D56">
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G56" t="b">
         <v>0</v>
@@ -2520,25 +2517,25 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G57" t="b">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -2546,13 +2543,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
         <v>80</v>
-      </c>
-      <c r="B58">
-        <v>8</v>
-      </c>
-      <c r="C58" t="s">
-        <v>81</v>
       </c>
       <c r="D58">
         <v>4</v>
@@ -2569,13 +2566,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B59">
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -2592,19 +2589,19 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>79</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
         <v>80</v>
       </c>
-      <c r="B60">
-        <v>8</v>
-      </c>
-      <c r="C60" t="s">
-        <v>81</v>
-      </c>
       <c r="D60">
         <v>4</v>
       </c>
       <c r="E60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
@@ -2615,19 +2612,19 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B61">
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D61">
         <v>4</v>
       </c>
       <c r="E61" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G61" t="b">
         <v>0</v>
@@ -2638,19 +2635,19 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
         <v>80</v>
       </c>
-      <c r="B62">
-        <v>8</v>
-      </c>
-      <c r="C62" t="s">
-        <v>81</v>
-      </c>
       <c r="D62">
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G62" t="b">
         <v>0</v>
@@ -2661,19 +2658,19 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B63">
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D63">
         <v>4</v>
       </c>
       <c r="E63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G63" t="b">
         <v>0</v>
@@ -2684,13 +2681,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64" t="s">
         <v>80</v>
-      </c>
-      <c r="B64">
-        <v>8</v>
-      </c>
-      <c r="C64" t="s">
-        <v>81</v>
       </c>
       <c r="D64">
         <v>4</v>
@@ -2707,13 +2704,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B65">
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D65">
         <v>4</v>
@@ -2722,7 +2719,7 @@
         <v>4321</v>
       </c>
       <c r="F65" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G65" t="b">
         <v>0</v>

--- a/excel/butterScaler/butterScaler23-Section02.xlsx
+++ b/excel/butterScaler/butterScaler23-Section02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0EBDD5-B6DE-F54C-BF72-E76D926122CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B456A3-0440-AB4A-B8F2-D036223964EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-12200" yWindow="-28200" windowWidth="27580" windowHeight="28200" xr2:uid="{BAFFE9DA-3B16-ED42-8F62-B38F2EE3FAD2}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="88">
   <si>
     <t>ActionName</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>结束</t>
   </si>
 </sst>
 </file>
@@ -2722,7 +2725,10 @@
         <v>86</v>
       </c>
       <c r="G65" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>87</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
